--- a/nr-update-system-nss/ig/ValueSet-fr-core-vs-categorie-sae-etablissement.xlsx
+++ b/nr-update-system-nss/ig/ValueSet-fr-core-vs-categorie-sae-etablissement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Catégrorie d'établissement de santé, suivant les valeurs de la SAE (Structure d'Activité d'Etablissement) 2024</t>
+    <t>Catérorie d'établissement de santé, suivant les valeurs de la SAE (Structure d'Activité d'Etablissement) 2024</t>
   </si>
   <si>
     <t>Purpose</t>
